--- a/build/temp/pages/StructureDefinition-cibmtr-vital-signs.xlsx
+++ b/build/temp/pages/StructureDefinition-cibmtr-vital-signs.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.8</t>
+    <t>0.1.9</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:55:04-06:00</t>
+    <t>2025-09-19T15:08:00-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1289,7 +1289,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitioner|http://hl7.org/fhir/us/core/StructureDefinition/us-core-organization|http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient|PractitionerRole|http://hl7.org/fhir/us/core/StructureDefinition/us-core-careteam|http://hl7.org/fhir/us/core/StructureDefinition/us-core-relatedperson)
 </t>
   </si>
   <si>
@@ -2200,17 +2200,17 @@
   <dimension ref="A1:AP83"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="52.9609375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="43.60546875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.57421875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.81640625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.90234375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.69921875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.625" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.98828125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="47.49609375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="39.10546875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="14.8671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.8125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.55078125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="111.63671875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2219,28 +2219,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.84375" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.71484375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.08984375" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.078125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.3125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="95.77734375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="63.8046875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.69140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.92578125" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0390625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.98828125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.3046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="40.19140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.5" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.87890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.93359375" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.08984375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="85.89453125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="57.22265625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.8671875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="35.90625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.44140625" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.03515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="36.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.51953125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.859375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="26.71875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="239.703125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="23.9609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="214.97265625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="103.87890625" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="32.84375" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="37.7109375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="93.1640625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="29.45703125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="33.8203125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8648,7 +8648,7 @@
         <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>21</v>

--- a/build/temp/pages/StructureDefinition-cibmtr-vital-signs.xlsx
+++ b/build/temp/pages/StructureDefinition-cibmtr-vital-signs.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$79</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3217" uniqueCount="595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3063" uniqueCount="591">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.9</t>
+    <t>0.1.10</t>
   </si>
   <si>
     <t>Name</t>
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>CIBMTR Vital Signs Results Profile (us-core)</t>
+    <t>CIBMTR Vital Signs Results Profile (US Core)</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-19T15:08:00-05:00</t>
+    <t>2026-04-23T10:10:52-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -452,7 +452,7 @@
     <t>Observation.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -490,7 +490,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">pattern:system}
@@ -680,7 +680,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -1098,10 +1098,7 @@
     <t>5. SHALL contain exactly one [1..1] code, where the @code SHOULD be selected from ValueSet HITSP Vital Sign Result Type 2.16.840.1.113883.3.88.12.80.62 DYNAMIC (CONF:7301).</t>
   </si>
   <si>
-    <t>Vital sign result types</t>
-  </si>
-  <si>
-    <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113883.3.88.12.80.62</t>
+    <t>https://vsac.nlm.nih.gov/valueset/2.16.840.1.113762.1.4.1295.1/expansion</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1120,21 +1117,6 @@
   </si>
   <si>
     <t>116680003 |Is a|</t>
-  </si>
-  <si>
-    <t>Observation.code.id</t>
-  </si>
-  <si>
-    <t>Observation.code.extension</t>
-  </si>
-  <si>
-    <t>Observation.code.coding</t>
-  </si>
-  <si>
-    <t>http://fhir.nmdp.org/ig/cibmtr-reporting/ValueSet/vital-signs</t>
-  </si>
-  <si>
-    <t>Observation.code.text</t>
   </si>
   <si>
     <t>Observation.subject</t>
@@ -1317,8 +1299,8 @@
     <t>Observation.value[x]</t>
   </si>
   <si>
-    <t>Quantity
-CodeableConcept</t>
+    <t xml:space="preserve">Quantity
+</t>
   </si>
   <si>
     <t>Vital Signs Value</t>
@@ -1817,6 +1799,12 @@
   </si>
   <si>
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
+  </si>
+  <si>
+    <t>Vital sign result types</t>
+  </si>
+  <si>
+    <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113883.3.88.12.80.62</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR @@ -2126,9 +2114,7 @@
       <c r="A13" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="B13" t="s" s="2">
-        <v>9</v>
-      </c>
+      <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
@@ -2197,7 +2183,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP83"/>
+  <dimension ref="A1:AP79"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="47.49609375" customWidth="true" bestFit="true"/>
@@ -2225,7 +2211,7 @@
     <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="85.89453125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="57.22265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="61.6875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.8671875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="35.90625" customWidth="true" bestFit="true"/>
@@ -3567,7 +3553,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>156</v>
       </c>
@@ -5733,7 +5719,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>280</v>
       </c>
@@ -5973,7 +5959,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>303</v>
       </c>
@@ -6335,7 +6321,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
         <v>309</v>
       </c>
@@ -6695,7 +6681,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
         <v>322</v>
       </c>
@@ -6937,7 +6923,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
         <v>327</v>
       </c>
@@ -7421,7 +7407,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
         <v>343</v>
       </c>
@@ -7488,11 +7474,9 @@
       <c r="X44" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="Y44" t="s" s="2">
+      <c r="Y44" s="2"/>
+      <c r="Z44" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>21</v>
@@ -7525,30 +7509,30 @@
         <v>104</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AL44" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="AL44" t="s" s="2">
+      <c r="AM44" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="AM44" t="s" s="2">
+      <c r="AN44" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="AN44" t="s" s="2">
+      <c r="AO44" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AO44" t="s" s="2">
+      <c r="AP44" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AP44" t="s" s="2">
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
         <v>356</v>
       </c>
-    </row>
-    <row r="45" hidden="true">
-      <c r="A45" t="s" s="2">
-        <v>357</v>
-      </c>
       <c r="B45" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7556,31 +7540,35 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>106</v>
+        <v>357</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>107</v>
+        <v>358</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+        <v>359</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>21</v>
       </c>
@@ -7628,7 +7616,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>109</v>
+        <v>356</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7640,22 +7628,22 @@
         <v>21</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>21</v>
+        <v>362</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>21</v>
+        <v>363</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>110</v>
+        <v>364</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>21</v>
+        <v>365</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>21</v>
@@ -7663,14 +7651,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7686,19 +7674,19 @@
         <v>21</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>113</v>
+        <v>367</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>114</v>
+        <v>368</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>115</v>
+        <v>369</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>116</v>
+        <v>370</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7736,19 +7724,19 @@
         <v>21</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>118</v>
+        <v>21</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>119</v>
+        <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>120</v>
+        <v>366</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7760,7 +7748,7 @@
         <v>21</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>21</v>
@@ -7769,13 +7757,13 @@
         <v>21</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>21</v>
+        <v>352</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>110</v>
+        <v>371</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>21</v>
+        <v>365</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>21</v>
@@ -7783,21 +7771,21 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>21</v>
+        <v>373</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>21</v>
@@ -7809,19 +7797,19 @@
         <v>93</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>146</v>
+        <v>374</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>311</v>
+        <v>375</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>312</v>
+        <v>376</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>313</v>
+        <v>377</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>314</v>
+        <v>378</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>21</v>
@@ -7846,11 +7834,13 @@
         <v>21</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="Y47" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z47" t="s" s="2">
-        <v>360</v>
+        <v>21</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>21</v>
@@ -7868,13 +7858,13 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>315</v>
+        <v>372</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>21</v>
@@ -7883,44 +7873,44 @@
         <v>104</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>21</v>
+        <v>379</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>316</v>
+        <v>380</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>317</v>
+        <v>381</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>21</v>
+        <v>382</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>361</v>
+        <v>383</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>361</v>
+        <v>383</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>21</v>
+        <v>384</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>21</v>
@@ -7929,19 +7919,19 @@
         <v>93</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>106</v>
+        <v>385</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>336</v>
+        <v>386</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>337</v>
+        <v>387</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>338</v>
+        <v>388</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>339</v>
+        <v>389</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>21</v>
@@ -7990,7 +7980,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>340</v>
+        <v>383</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7999,25 +7989,25 @@
         <v>92</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>21</v>
+        <v>390</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>104</v>
+        <v>391</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>21</v>
+        <v>392</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>341</v>
+        <v>393</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>342</v>
+        <v>394</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>21</v>
+        <v>395</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>21</v>
@@ -8025,10 +8015,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>362</v>
+        <v>396</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>362</v>
+        <v>396</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8036,13 +8026,13 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>21</v>
@@ -8051,20 +8041,18 @@
         <v>93</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>363</v>
+        <v>128</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>364</v>
+        <v>397</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>365</v>
+        <v>398</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>367</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>21</v>
       </c>
@@ -8112,7 +8100,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>362</v>
+        <v>396</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8127,30 +8115,30 @@
         <v>104</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>368</v>
+        <v>21</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>369</v>
+        <v>400</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>370</v>
+        <v>401</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>372</v>
+        <v>403</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>372</v>
+        <v>403</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8164,7 +8152,7 @@
         <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>21</v>
@@ -8173,18 +8161,18 @@
         <v>93</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>373</v>
+        <v>404</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>374</v>
+        <v>405</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="O50" s="2"/>
+        <v>406</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>21</v>
       </c>
@@ -8232,7 +8220,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>372</v>
+        <v>403</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8247,34 +8235,34 @@
         <v>104</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>21</v>
+        <v>408</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>353</v>
+        <v>409</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>377</v>
+        <v>410</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>371</v>
+        <v>411</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
-        <v>378</v>
+        <v>412</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>378</v>
+        <v>412</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>379</v>
+        <v>21</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8284,7 +8272,7 @@
         <v>92</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>21</v>
@@ -8293,19 +8281,19 @@
         <v>93</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>380</v>
+        <v>413</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>381</v>
+        <v>414</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>382</v>
+        <v>415</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>383</v>
+        <v>416</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>384</v>
+        <v>417</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>21</v>
@@ -8330,13 +8318,13 @@
         <v>21</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>21</v>
+        <v>150</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>21</v>
+        <v>418</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>21</v>
+        <v>419</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>21</v>
@@ -8354,7 +8342,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>378</v>
+        <v>412</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8363,44 +8351,44 @@
         <v>92</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>21</v>
+        <v>420</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>385</v>
+        <v>21</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>21</v>
+        <v>421</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>386</v>
+        <v>422</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>387</v>
+        <v>423</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>388</v>
+        <v>21</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>21</v>
+        <v>424</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>389</v>
+        <v>425</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>389</v>
+        <v>425</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>390</v>
+        <v>21</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>92</v>
@@ -8412,22 +8400,22 @@
         <v>21</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>391</v>
+        <v>293</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>392</v>
+        <v>426</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>393</v>
+        <v>427</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>394</v>
+        <v>428</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>395</v>
+        <v>429</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>21</v>
@@ -8452,13 +8440,13 @@
         <v>21</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>21</v>
+        <v>150</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>21</v>
+        <v>430</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>21</v>
+        <v>431</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>21</v>
@@ -8476,7 +8464,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>389</v>
+        <v>425</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8485,25 +8473,25 @@
         <v>92</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>396</v>
+        <v>432</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>397</v>
+        <v>104</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>398</v>
+        <v>21</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>399</v>
+        <v>244</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>400</v>
+        <v>433</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>401</v>
+        <v>21</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>21</v>
@@ -8511,21 +8499,21 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>402</v>
+        <v>434</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>402</v>
+        <v>434</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>21</v>
+        <v>435</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>21</v>
@@ -8534,21 +8522,23 @@
         <v>21</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>128</v>
+        <v>293</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>403</v>
+        <v>436</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>404</v>
+        <v>437</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="O53" s="2"/>
+        <v>438</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>439</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>21</v>
       </c>
@@ -8572,13 +8562,13 @@
         <v>21</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>21</v>
+        <v>150</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>21</v>
+        <v>440</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>21</v>
+        <v>441</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>21</v>
@@ -8596,13 +8586,13 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>402</v>
+        <v>434</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>21</v>
@@ -8614,27 +8604,27 @@
         <v>21</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>21</v>
+        <v>442</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>406</v>
+        <v>443</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>407</v>
+        <v>444</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>408</v>
+        <v>21</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>21</v>
+        <v>445</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>409</v>
+        <v>446</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>409</v>
+        <v>446</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8648,26 +8638,28 @@
         <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>410</v>
+        <v>447</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>411</v>
+        <v>448</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>449</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>450</v>
+      </c>
       <c r="O54" t="s" s="2">
-        <v>413</v>
+        <v>451</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>21</v>
@@ -8716,7 +8708,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>409</v>
+        <v>446</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8731,19 +8723,19 @@
         <v>104</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>414</v>
+        <v>21</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>415</v>
+        <v>452</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>416</v>
+        <v>453</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>417</v>
+        <v>21</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>21</v>
@@ -8751,10 +8743,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>418</v>
+        <v>454</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>418</v>
+        <v>454</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8768,29 +8760,27 @@
         <v>92</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>419</v>
+        <v>293</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>420</v>
+        <v>455</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>421</v>
+        <v>456</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>423</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>21</v>
       </c>
@@ -8814,13 +8804,13 @@
         <v>21</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>150</v>
+        <v>212</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>424</v>
+        <v>458</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>425</v>
+        <v>459</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>21</v>
@@ -8838,7 +8828,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>418</v>
+        <v>454</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8847,7 +8837,7 @@
         <v>92</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>426</v>
+        <v>21</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>104</v>
@@ -8856,27 +8846,27 @@
         <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>427</v>
+        <v>460</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>428</v>
+        <v>461</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>429</v>
+        <v>462</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>430</v>
+        <v>463</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>431</v>
+        <v>464</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>431</v>
+        <v>464</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8890,7 +8880,7 @@
         <v>92</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>21</v>
@@ -8902,16 +8892,16 @@
         <v>293</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>432</v>
+        <v>465</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>433</v>
+        <v>466</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>21</v>
@@ -8936,13 +8926,13 @@
         <v>21</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>150</v>
+        <v>212</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>436</v>
+        <v>469</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>437</v>
+        <v>470</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>21</v>
@@ -8960,7 +8950,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>431</v>
+        <v>464</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8969,7 +8959,7 @@
         <v>92</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>438</v>
+        <v>21</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>104</v>
@@ -8981,10 +8971,10 @@
         <v>21</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>244</v>
+        <v>471</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>439</v>
+        <v>472</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>21</v>
@@ -8995,21 +8985,21 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>440</v>
+        <v>473</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>440</v>
+        <v>473</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>441</v>
+        <v>21</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>21</v>
@@ -9021,20 +9011,18 @@
         <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>293</v>
+        <v>474</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>442</v>
+        <v>475</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>443</v>
+        <v>476</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>445</v>
-      </c>
+        <v>477</v>
+      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>21</v>
       </c>
@@ -9058,13 +9046,13 @@
         <v>21</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>150</v>
+        <v>21</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>447</v>
+        <v>21</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>21</v>
@@ -9082,13 +9070,13 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>440</v>
+        <v>473</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>21</v>
@@ -9100,27 +9088,27 @@
         <v>21</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>448</v>
+        <v>478</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>449</v>
+        <v>479</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>450</v>
+        <v>480</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>451</v>
+        <v>481</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>452</v>
+        <v>482</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>452</v>
+        <v>482</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9131,7 +9119,7 @@
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>21</v>
@@ -9143,20 +9131,18 @@
         <v>21</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>453</v>
+        <v>483</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>454</v>
+        <v>484</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>455</v>
+        <v>485</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>457</v>
-      </c>
+        <v>486</v>
+      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>21</v>
       </c>
@@ -9204,13 +9190,13 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>452</v>
+        <v>482</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>21</v>
@@ -9222,27 +9208,27 @@
         <v>21</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>21</v>
+        <v>487</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>458</v>
+        <v>488</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>459</v>
+        <v>489</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>21</v>
+        <v>490</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>460</v>
+        <v>491</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>460</v>
+        <v>491</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9253,7 +9239,7 @@
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>21</v>
@@ -9265,18 +9251,20 @@
         <v>21</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>293</v>
+        <v>492</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>461</v>
+        <v>493</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>462</v>
+        <v>494</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>495</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>21</v>
       </c>
@@ -9300,13 +9288,13 @@
         <v>21</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>212</v>
+        <v>21</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>464</v>
+        <v>21</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>465</v>
+        <v>21</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>21</v>
@@ -9324,45 +9312,45 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>460</v>
+        <v>491</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>104</v>
+        <v>497</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>466</v>
+        <v>21</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>467</v>
+        <v>498</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>468</v>
+        <v>499</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>469</v>
+        <v>21</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>470</v>
+        <v>500</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>470</v>
+        <v>500</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9385,20 +9373,16 @@
         <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>293</v>
+        <v>106</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>471</v>
+        <v>107</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>474</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>21</v>
       </c>
@@ -9422,13 +9406,13 @@
         <v>21</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>212</v>
+        <v>21</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>475</v>
+        <v>21</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>476</v>
+        <v>21</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>21</v>
@@ -9446,7 +9430,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>470</v>
+        <v>109</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9458,7 +9442,7 @@
         <v>21</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>21</v>
@@ -9467,10 +9451,10 @@
         <v>21</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>477</v>
+        <v>21</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>478</v>
+        <v>110</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>21</v>
@@ -9481,21 +9465,21 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>479</v>
+        <v>501</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>479</v>
+        <v>501</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>21</v>
@@ -9507,16 +9491,16 @@
         <v>21</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>480</v>
+        <v>113</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>481</v>
+        <v>114</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>482</v>
+        <v>115</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>483</v>
+        <v>116</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9566,79 +9550,81 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>479</v>
+        <v>120</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>484</v>
+        <v>21</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>485</v>
+        <v>21</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>486</v>
+        <v>110</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>487</v>
+        <v>21</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>488</v>
+        <v>502</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>488</v>
+        <v>502</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>21</v>
+        <v>503</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>489</v>
+        <v>113</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>490</v>
+        <v>504</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>491</v>
+        <v>505</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>21</v>
       </c>
@@ -9686,45 +9672,45 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>488</v>
+        <v>506</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>493</v>
+        <v>21</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>494</v>
+        <v>21</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>495</v>
+        <v>244</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>496</v>
+        <v>21</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9735,7 +9721,7 @@
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>21</v>
@@ -9747,20 +9733,16 @@
         <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>498</v>
+        <v>508</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>499</v>
+        <v>509</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>502</v>
-      </c>
+        <v>510</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>21</v>
       </c>
@@ -9808,19 +9790,19 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>21</v>
+        <v>511</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>503</v>
+        <v>104</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>21</v>
@@ -9829,10 +9811,10 @@
         <v>21</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>21</v>
@@ -9843,10 +9825,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9869,13 +9851,13 @@
         <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>106</v>
+        <v>508</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>107</v>
+        <v>515</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>108</v>
+        <v>516</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9926,7 +9908,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>109</v>
+        <v>514</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9935,10 +9917,10 @@
         <v>92</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>21</v>
+        <v>511</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>21</v>
@@ -9947,10 +9929,10 @@
         <v>21</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>21</v>
+        <v>512</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>110</v>
+        <v>517</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>21</v>
@@ -9961,21 +9943,21 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>507</v>
+        <v>518</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>507</v>
+        <v>518</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>21</v>
@@ -9987,18 +9969,20 @@
         <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>113</v>
+        <v>293</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>114</v>
+        <v>519</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>115</v>
+        <v>520</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="O65" s="2"/>
+        <v>521</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>522</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>21</v>
       </c>
@@ -10022,13 +10006,13 @@
         <v>21</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>21</v>
+        <v>225</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>21</v>
+        <v>523</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>21</v>
+        <v>524</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>21</v>
@@ -10046,31 +10030,31 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>120</v>
+        <v>518</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>21</v>
+        <v>525</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>21</v>
+        <v>526</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>110</v>
+        <v>444</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>21</v>
@@ -10081,14 +10065,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>508</v>
+        <v>527</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>508</v>
+        <v>527</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>509</v>
+        <v>21</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10101,25 +10085,25 @@
         <v>21</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>113</v>
+        <v>293</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>510</v>
+        <v>528</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>511</v>
+        <v>529</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>116</v>
+        <v>530</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>251</v>
+        <v>531</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>21</v>
@@ -10144,13 +10128,13 @@
         <v>21</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>21</v>
+        <v>212</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>21</v>
+        <v>532</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>21</v>
+        <v>533</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>21</v>
@@ -10168,7 +10152,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>512</v>
+        <v>527</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10180,19 +10164,19 @@
         <v>21</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>21</v>
+        <v>525</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>21</v>
+        <v>526</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>244</v>
+        <v>444</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>21</v>
@@ -10203,10 +10187,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>513</v>
+        <v>534</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>513</v>
+        <v>534</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10229,16 +10213,18 @@
         <v>21</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>514</v>
+        <v>535</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>515</v>
+        <v>536</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>516</v>
+        <v>537</v>
       </c>
       <c r="N67" s="2"/>
-      <c r="O67" s="2"/>
+      <c r="O67" t="s" s="2">
+        <v>538</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>21</v>
       </c>
@@ -10286,7 +10272,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>513</v>
+        <v>534</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10295,7 +10281,7 @@
         <v>92</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>517</v>
+        <v>21</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>104</v>
@@ -10307,10 +10293,10 @@
         <v>21</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>518</v>
+        <v>21</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>519</v>
+        <v>539</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>21</v>
@@ -10321,10 +10307,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10347,13 +10333,13 @@
         <v>21</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>514</v>
+        <v>106</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>521</v>
+        <v>541</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>522</v>
+        <v>542</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10404,7 +10390,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10413,7 +10399,7 @@
         <v>92</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>517</v>
+        <v>21</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>104</v>
@@ -10425,10 +10411,10 @@
         <v>21</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>523</v>
+        <v>543</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>21</v>
@@ -10439,10 +10425,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>524</v>
+        <v>544</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>524</v>
+        <v>544</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10453,7 +10439,7 @@
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>21</v>
@@ -10462,23 +10448,21 @@
         <v>21</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>293</v>
+        <v>545</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>525</v>
+        <v>546</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>526</v>
+        <v>547</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>528</v>
-      </c>
+        <v>548</v>
+      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>21</v>
       </c>
@@ -10502,13 +10486,13 @@
         <v>21</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>225</v>
+        <v>21</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>529</v>
+        <v>21</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>530</v>
+        <v>21</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>21</v>
@@ -10526,13 +10510,13 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>524</v>
+        <v>544</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>21</v>
@@ -10544,13 +10528,13 @@
         <v>21</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>531</v>
+        <v>21</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>532</v>
+        <v>549</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>450</v>
+        <v>550</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>21</v>
@@ -10561,10 +10545,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>533</v>
+        <v>551</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>533</v>
+        <v>551</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10584,23 +10568,21 @@
         <v>21</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>293</v>
+        <v>552</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>534</v>
+        <v>553</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>535</v>
+        <v>554</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>537</v>
-      </c>
+        <v>555</v>
+      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>21</v>
       </c>
@@ -10624,13 +10606,13 @@
         <v>21</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>212</v>
+        <v>21</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>538</v>
+        <v>21</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>539</v>
+        <v>21</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>21</v>
@@ -10648,7 +10630,7 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>533</v>
+        <v>551</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10666,13 +10648,13 @@
         <v>21</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>531</v>
+        <v>21</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>532</v>
+        <v>549</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>450</v>
+        <v>556</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>21</v>
@@ -10681,12 +10663,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
-        <v>540</v>
+        <v>557</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>540</v>
+        <v>557</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10697,29 +10679,31 @@
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>541</v>
+        <v>492</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>542</v>
+        <v>558</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="N71" s="2"/>
+        <v>559</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>560</v>
+      </c>
       <c r="O71" t="s" s="2">
-        <v>544</v>
+        <v>561</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>21</v>
@@ -10768,19 +10752,19 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>540</v>
+        <v>557</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>104</v>
+        <v>562</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>21</v>
@@ -10789,10 +10773,10 @@
         <v>21</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>21</v>
+        <v>563</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>545</v>
+        <v>564</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>21</v>
@@ -10803,10 +10787,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>546</v>
+        <v>565</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>546</v>
+        <v>565</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10832,10 +10816,10 @@
         <v>106</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>547</v>
+        <v>107</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>548</v>
+        <v>108</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10886,7 +10870,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>546</v>
+        <v>109</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10898,7 +10882,7 @@
         <v>21</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>21</v>
@@ -10907,10 +10891,10 @@
         <v>21</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>518</v>
+        <v>21</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>549</v>
+        <v>110</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>21</v>
@@ -10921,14 +10905,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>550</v>
+        <v>566</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>550</v>
+        <v>566</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10944,19 +10928,19 @@
         <v>21</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>551</v>
+        <v>113</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>552</v>
+        <v>114</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>553</v>
+        <v>115</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>554</v>
+        <v>116</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11006,7 +10990,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>550</v>
+        <v>120</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11018,7 +11002,7 @@
         <v>21</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>21</v>
@@ -11027,10 +11011,10 @@
         <v>21</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>555</v>
+        <v>21</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>556</v>
+        <v>110</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>21</v>
@@ -11041,14 +11025,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>557</v>
+        <v>567</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>557</v>
+        <v>567</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>21</v>
+        <v>503</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11061,24 +11045,26 @@
         <v>21</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="J74" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>558</v>
+        <v>113</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>559</v>
+        <v>504</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>560</v>
+        <v>505</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="O74" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>21</v>
       </c>
@@ -11126,7 +11112,7 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>557</v>
+        <v>506</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11138,7 +11124,7 @@
         <v>21</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>21</v>
@@ -11147,10 +11133,10 @@
         <v>21</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>555</v>
+        <v>21</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>562</v>
+        <v>244</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>21</v>
@@ -11159,12 +11145,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="75" hidden="true">
+    <row r="75">
       <c r="A75" t="s" s="2">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11172,10 +11158,10 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>93</v>
@@ -11187,19 +11173,19 @@
         <v>93</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>498</v>
+        <v>293</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>564</v>
+        <v>345</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>21</v>
@@ -11224,13 +11210,13 @@
         <v>21</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>21</v>
+        <v>150</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>21</v>
+        <v>572</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>21</v>
+        <v>573</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>21</v>
@@ -11248,45 +11234,45 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>568</v>
+        <v>104</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>21</v>
+        <v>574</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>569</v>
+        <v>352</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>570</v>
+        <v>353</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>21</v>
+        <v>354</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="76" hidden="true">
+    <row r="76">
       <c r="A76" t="s" s="2">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11300,25 +11286,29 @@
         <v>92</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>106</v>
+        <v>576</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>107</v>
+        <v>577</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
+        <v>578</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>417</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>21</v>
       </c>
@@ -11342,13 +11332,13 @@
         <v>21</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>21</v>
+        <v>150</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>21</v>
+        <v>418</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>21</v>
+        <v>419</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>21</v>
@@ -11366,7 +11356,7 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>109</v>
+        <v>575</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11375,50 +11365,50 @@
         <v>92</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>21</v>
+        <v>580</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>21</v>
+        <v>581</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>21</v>
+        <v>422</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>110</v>
+        <v>423</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>21</v>
+        <v>424</v>
       </c>
     </row>
-    <row r="77" hidden="true">
+    <row r="77">
       <c r="A77" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>21</v>
@@ -11427,18 +11417,20 @@
         <v>21</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>113</v>
+        <v>293</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>114</v>
+        <v>583</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>115</v>
+        <v>584</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="O77" s="2"/>
+        <v>585</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>429</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>21</v>
       </c>
@@ -11462,13 +11454,13 @@
         <v>21</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>21</v>
+        <v>150</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>21</v>
+        <v>430</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>21</v>
+        <v>431</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>21</v>
@@ -11486,19 +11478,19 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>120</v>
+        <v>582</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>21</v>
+        <v>586</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>21</v>
@@ -11507,10 +11499,10 @@
         <v>21</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>21</v>
+        <v>244</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>110</v>
+        <v>433</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>21</v>
@@ -11521,14 +11513,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>573</v>
+        <v>587</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>573</v>
+        <v>587</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>509</v>
+        <v>435</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -11541,25 +11533,25 @@
         <v>21</v>
       </c>
       <c r="I78" t="s" s="2">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>113</v>
+        <v>293</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>510</v>
+        <v>436</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>511</v>
+        <v>437</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>116</v>
+        <v>438</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>251</v>
+        <v>439</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>21</v>
@@ -11584,13 +11576,13 @@
         <v>21</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>21</v>
+        <v>150</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>21</v>
+        <v>440</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>21</v>
+        <v>441</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>21</v>
@@ -11608,7 +11600,7 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>512</v>
+        <v>587</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11620,33 +11612,33 @@
         <v>21</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>21</v>
+        <v>442</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>21</v>
+        <v>443</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>244</v>
+        <v>444</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>21</v>
+        <v>445</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>574</v>
+        <v>588</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>574</v>
+        <v>588</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11654,34 +11646,34 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>293</v>
+        <v>82</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>345</v>
+        <v>589</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>575</v>
+        <v>590</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>576</v>
+        <v>495</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>577</v>
+        <v>496</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>21</v>
@@ -11706,13 +11698,13 @@
         <v>21</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>150</v>
+        <v>21</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>349</v>
+        <v>21</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>350</v>
+        <v>21</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>21</v>
@@ -11730,13 +11722,13 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>574</v>
+        <v>588</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>21</v>
@@ -11748,521 +11740,33 @@
         <v>21</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>578</v>
+        <v>21</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>353</v>
+        <v>498</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>354</v>
+        <v>499</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>355</v>
+        <v>21</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="80" hidden="true">
-      <c r="A80" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="C80" s="2"/>
-      <c r="D80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E80" s="2"/>
-      <c r="F80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G80" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H80" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="I80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J80" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="K80" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="L80" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="P80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q80" s="2"/>
-      <c r="R80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X80" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="Z80" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="AG80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH80" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI80" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="AJ80" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="AO80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP80" t="s" s="2">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="81" hidden="true">
-      <c r="A81" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="C81" s="2"/>
-      <c r="D81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E81" s="2"/>
-      <c r="F81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G81" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H81" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="I81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K81" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="L81" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="P81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q81" s="2"/>
-      <c r="R81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X81" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="AG81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH81" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI81" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="AJ81" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="AO81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP81" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="82" hidden="true">
-      <c r="A82" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="C82" s="2"/>
-      <c r="D82" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="E82" s="2"/>
-      <c r="F82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K82" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="L82" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="P82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q82" s="2"/>
-      <c r="R82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ82" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AO82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP82" t="s" s="2">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="83" hidden="true">
-      <c r="A83" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="C83" s="2"/>
-      <c r="D83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E83" s="2"/>
-      <c r="F83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="P83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q83" s="2"/>
-      <c r="R83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="AG83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ83" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP83" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP83">
-    <filterColumn colId="6">
+  <autoFilter ref="A1:AP79">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI82">
+  <conditionalFormatting sqref="A2:AI78">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/build/temp/pages/StructureDefinition-cibmtr-vital-signs.xlsx
+++ b/build/temp/pages/StructureDefinition-cibmtr-vital-signs.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$79</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3217" uniqueCount="595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3063" uniqueCount="591">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.9</t>
+    <t>0.1.11</t>
   </si>
   <si>
     <t>Name</t>
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>CIBMTR Vital Signs Results Profile (us-core)</t>
+    <t>CIBMTR Vital Signs Results Profile (US Core)</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-19T15:08:00-05:00</t>
+    <t>2026-06-10T07:35:08-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -452,7 +452,7 @@
     <t>Observation.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -490,7 +490,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">pattern:system}
@@ -680,7 +680,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -1098,10 +1098,7 @@
     <t>5. SHALL contain exactly one [1..1] code, where the @code SHOULD be selected from ValueSet HITSP Vital Sign Result Type 2.16.840.1.113883.3.88.12.80.62 DYNAMIC (CONF:7301).</t>
   </si>
   <si>
-    <t>Vital sign result types</t>
-  </si>
-  <si>
-    <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113883.3.88.12.80.62</t>
+    <t>https://vsac.nlm.nih.gov/valueset/2.16.840.1.113762.1.4.1295.1/expansion</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1120,21 +1117,6 @@
   </si>
   <si>
     <t>116680003 |Is a|</t>
-  </si>
-  <si>
-    <t>Observation.code.id</t>
-  </si>
-  <si>
-    <t>Observation.code.extension</t>
-  </si>
-  <si>
-    <t>Observation.code.coding</t>
-  </si>
-  <si>
-    <t>http://fhir.nmdp.org/ig/cibmtr-reporting/ValueSet/vital-signs</t>
-  </si>
-  <si>
-    <t>Observation.code.text</t>
   </si>
   <si>
     <t>Observation.subject</t>
@@ -1317,8 +1299,8 @@
     <t>Observation.value[x]</t>
   </si>
   <si>
-    <t>Quantity
-CodeableConcept</t>
+    <t xml:space="preserve">Quantity
+</t>
   </si>
   <si>
     <t>Vital Signs Value</t>
@@ -1817,6 +1799,12 @@
   </si>
   <si>
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
+  </si>
+  <si>
+    <t>Vital sign result types</t>
+  </si>
+  <si>
+    <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113883.3.88.12.80.62</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR @@ -2126,9 +2114,7 @@
       <c r="A13" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="B13" t="s" s="2">
-        <v>9</v>
-      </c>
+      <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
@@ -2197,7 +2183,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP83"/>
+  <dimension ref="A1:AP79"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="47.49609375" customWidth="true" bestFit="true"/>
@@ -2225,7 +2211,7 @@
     <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="85.89453125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="57.22265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="61.6875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.8671875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="35.90625" customWidth="true" bestFit="true"/>
@@ -3567,7 +3553,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>156</v>
       </c>
@@ -5733,7 +5719,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>280</v>
       </c>
@@ -5973,7 +5959,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>303</v>
       </c>
@@ -6335,7 +6321,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
         <v>309</v>
       </c>
@@ -6695,7 +6681,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
         <v>322</v>
       </c>
@@ -6937,7 +6923,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
         <v>327</v>
       </c>
@@ -7421,7 +7407,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
         <v>343</v>
       </c>
@@ -7488,11 +7474,9 @@
       <c r="X44" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="Y44" t="s" s="2">
+      <c r="Y44" s="2"/>
+      <c r="Z44" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>21</v>
@@ -7525,30 +7509,30 @@
         <v>104</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AL44" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="AL44" t="s" s="2">
+      <c r="AM44" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="AM44" t="s" s="2">
+      <c r="AN44" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="AN44" t="s" s="2">
+      <c r="AO44" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AO44" t="s" s="2">
+      <c r="AP44" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AP44" t="s" s="2">
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
         <v>356</v>
       </c>
-    </row>
-    <row r="45" hidden="true">
-      <c r="A45" t="s" s="2">
-        <v>357</v>
-      </c>
       <c r="B45" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7556,31 +7540,35 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>106</v>
+        <v>357</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>107</v>
+        <v>358</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+        <v>359</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>21</v>
       </c>
@@ -7628,7 +7616,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>109</v>
+        <v>356</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7640,22 +7628,22 @@
         <v>21</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>21</v>
+        <v>362</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>21</v>
+        <v>363</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>110</v>
+        <v>364</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>21</v>
+        <v>365</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>21</v>
@@ -7663,14 +7651,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7686,19 +7674,19 @@
         <v>21</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>113</v>
+        <v>367</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>114</v>
+        <v>368</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>115</v>
+        <v>369</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>116</v>
+        <v>370</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7736,19 +7724,19 @@
         <v>21</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>118</v>
+        <v>21</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>119</v>
+        <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>120</v>
+        <v>366</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7760,7 +7748,7 @@
         <v>21</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>21</v>
@@ -7769,13 +7757,13 @@
         <v>21</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>21</v>
+        <v>352</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>110</v>
+        <v>371</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>21</v>
+        <v>365</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>21</v>
@@ -7783,21 +7771,21 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>21</v>
+        <v>373</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>21</v>
@@ -7809,19 +7797,19 @@
         <v>93</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>146</v>
+        <v>374</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>311</v>
+        <v>375</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>312</v>
+        <v>376</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>313</v>
+        <v>377</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>314</v>
+        <v>378</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>21</v>
@@ -7846,11 +7834,13 @@
         <v>21</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="Y47" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z47" t="s" s="2">
-        <v>360</v>
+        <v>21</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>21</v>
@@ -7868,13 +7858,13 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>315</v>
+        <v>372</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>21</v>
@@ -7883,44 +7873,44 @@
         <v>104</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>21</v>
+        <v>379</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>316</v>
+        <v>380</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>317</v>
+        <v>381</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>21</v>
+        <v>382</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>361</v>
+        <v>383</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>361</v>
+        <v>383</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>21</v>
+        <v>384</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>21</v>
@@ -7929,19 +7919,19 @@
         <v>93</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>106</v>
+        <v>385</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>336</v>
+        <v>386</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>337</v>
+        <v>387</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>338</v>
+        <v>388</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>339</v>
+        <v>389</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>21</v>
@@ -7990,7 +7980,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>340</v>
+        <v>383</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7999,25 +7989,25 @@
         <v>92</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>21</v>
+        <v>390</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>104</v>
+        <v>391</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>21</v>
+        <v>392</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>341</v>
+        <v>393</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>342</v>
+        <v>394</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>21</v>
+        <v>395</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>21</v>
@@ -8025,10 +8015,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>362</v>
+        <v>396</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>362</v>
+        <v>396</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8036,13 +8026,13 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>21</v>
@@ -8051,20 +8041,18 @@
         <v>93</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>363</v>
+        <v>128</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>364</v>
+        <v>397</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>365</v>
+        <v>398</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>367</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>21</v>
       </c>
@@ -8112,7 +8100,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>362</v>
+        <v>396</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8127,30 +8115,30 @@
         <v>104</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>368</v>
+        <v>21</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>369</v>
+        <v>400</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>370</v>
+        <v>401</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>372</v>
+        <v>403</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>372</v>
+        <v>403</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8164,7 +8152,7 @@
         <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>21</v>
@@ -8173,18 +8161,18 @@
         <v>93</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>373</v>
+        <v>404</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>374</v>
+        <v>405</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="O50" s="2"/>
+        <v>406</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>21</v>
       </c>
@@ -8232,7 +8220,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>372</v>
+        <v>403</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8247,34 +8235,34 @@
         <v>104</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>21</v>
+        <v>408</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>353</v>
+        <v>409</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>377</v>
+        <v>410</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>371</v>
+        <v>411</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
-        <v>378</v>
+        <v>412</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>378</v>
+        <v>412</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>379</v>
+        <v>21</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8284,7 +8272,7 @@
         <v>92</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>21</v>
@@ -8293,19 +8281,19 @@
         <v>93</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>380</v>
+        <v>413</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>381</v>
+        <v>414</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>382</v>
+        <v>415</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>383</v>
+        <v>416</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>384</v>
+        <v>417</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>21</v>
@@ -8330,13 +8318,13 @@
         <v>21</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>21</v>
+        <v>150</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>21</v>
+        <v>418</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>21</v>
+        <v>419</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>21</v>
@@ -8354,7 +8342,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>378</v>
+        <v>412</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8363,44 +8351,44 @@
         <v>92</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>21</v>
+        <v>420</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>385</v>
+        <v>21</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>21</v>
+        <v>421</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>386</v>
+        <v>422</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>387</v>
+        <v>423</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>388</v>
+        <v>21</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>21</v>
+        <v>424</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>389</v>
+        <v>425</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>389</v>
+        <v>425</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>390</v>
+        <v>21</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>92</v>
@@ -8412,22 +8400,22 @@
         <v>21</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>391</v>
+        <v>293</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>392</v>
+        <v>426</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>393</v>
+        <v>427</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>394</v>
+        <v>428</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>395</v>
+        <v>429</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>21</v>
@@ -8452,13 +8440,13 @@
         <v>21</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>21</v>
+        <v>150</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>21</v>
+        <v>430</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>21</v>
+        <v>431</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>21</v>
@@ -8476,7 +8464,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>389</v>
+        <v>425</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8485,25 +8473,25 @@
         <v>92</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>396</v>
+        <v>432</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>397</v>
+        <v>104</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>398</v>
+        <v>21</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>399</v>
+        <v>244</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>400</v>
+        <v>433</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>401</v>
+        <v>21</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>21</v>
@@ -8511,21 +8499,21 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>402</v>
+        <v>434</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>402</v>
+        <v>434</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>21</v>
+        <v>435</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>21</v>
@@ -8534,21 +8522,23 @@
         <v>21</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>128</v>
+        <v>293</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>403</v>
+        <v>436</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>404</v>
+        <v>437</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="O53" s="2"/>
+        <v>438</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>439</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>21</v>
       </c>
@@ -8572,13 +8562,13 @@
         <v>21</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>21</v>
+        <v>150</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>21</v>
+        <v>440</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>21</v>
+        <v>441</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>21</v>
@@ -8596,13 +8586,13 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>402</v>
+        <v>434</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>21</v>
@@ -8614,27 +8604,27 @@
         <v>21</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>21</v>
+        <v>442</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>406</v>
+        <v>443</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>407</v>
+        <v>444</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>408</v>
+        <v>21</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>21</v>
+        <v>445</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>409</v>
+        <v>446</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>409</v>
+        <v>446</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8648,26 +8638,28 @@
         <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>410</v>
+        <v>447</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>411</v>
+        <v>448</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>449</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>450</v>
+      </c>
       <c r="O54" t="s" s="2">
-        <v>413</v>
+        <v>451</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>21</v>
@@ -8716,7 +8708,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>409</v>
+        <v>446</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8731,19 +8723,19 @@
         <v>104</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>414</v>
+        <v>21</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>415</v>
+        <v>452</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>416</v>
+        <v>453</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>417</v>
+        <v>21</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>21</v>
@@ -8751,10 +8743,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>418</v>
+        <v>454</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>418</v>
+        <v>454</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8768,29 +8760,27 @@
         <v>92</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>419</v>
+        <v>293</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>420</v>
+        <v>455</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>421</v>
+        <v>456</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>423</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>21</v>
       </c>
@@ -8814,13 +8804,13 @@
         <v>21</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>150</v>
+        <v>212</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>424</v>
+        <v>458</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>425</v>
+        <v>459</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>21</v>
@@ -8838,7 +8828,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>418</v>
+        <v>454</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8847,7 +8837,7 @@
         <v>92</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>426</v>
+        <v>21</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>104</v>
@@ -8856,27 +8846,27 @@
         <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>427</v>
+        <v>460</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>428</v>
+        <v>461</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>429</v>
+        <v>462</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>430</v>
+        <v>463</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>431</v>
+        <v>464</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>431</v>
+        <v>464</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8890,7 +8880,7 @@
         <v>92</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>21</v>
@@ -8902,16 +8892,16 @@
         <v>293</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>432</v>
+        <v>465</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>433</v>
+        <v>466</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>21</v>
@@ -8936,13 +8926,13 @@
         <v>21</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>150</v>
+        <v>212</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>436</v>
+        <v>469</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>437</v>
+        <v>470</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>21</v>
@@ -8960,7 +8950,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>431</v>
+        <v>464</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8969,7 +8959,7 @@
         <v>92</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>438</v>
+        <v>21</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>104</v>
@@ -8981,10 +8971,10 @@
         <v>21</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>244</v>
+        <v>471</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>439</v>
+        <v>472</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>21</v>
@@ -8995,21 +8985,21 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>440</v>
+        <v>473</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>440</v>
+        <v>473</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>441</v>
+        <v>21</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>21</v>
@@ -9021,20 +9011,18 @@
         <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>293</v>
+        <v>474</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>442</v>
+        <v>475</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>443</v>
+        <v>476</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>445</v>
-      </c>
+        <v>477</v>
+      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>21</v>
       </c>
@@ -9058,13 +9046,13 @@
         <v>21</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>150</v>
+        <v>21</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>447</v>
+        <v>21</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>21</v>
@@ -9082,13 +9070,13 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>440</v>
+        <v>473</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>21</v>
@@ -9100,27 +9088,27 @@
         <v>21</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>448</v>
+        <v>478</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>449</v>
+        <v>479</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>450</v>
+        <v>480</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>451</v>
+        <v>481</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>452</v>
+        <v>482</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>452</v>
+        <v>482</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9131,7 +9119,7 @@
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>21</v>
@@ -9143,20 +9131,18 @@
         <v>21</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>453</v>
+        <v>483</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>454</v>
+        <v>484</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>455</v>
+        <v>485</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>457</v>
-      </c>
+        <v>486</v>
+      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>21</v>
       </c>
@@ -9204,13 +9190,13 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>452</v>
+        <v>482</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>21</v>
@@ -9222,27 +9208,27 @@
         <v>21</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>21</v>
+        <v>487</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>458</v>
+        <v>488</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>459</v>
+        <v>489</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>21</v>
+        <v>490</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>460</v>
+        <v>491</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>460</v>
+        <v>491</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9253,7 +9239,7 @@
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>21</v>
@@ -9265,18 +9251,20 @@
         <v>21</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>293</v>
+        <v>492</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>461</v>
+        <v>493</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>462</v>
+        <v>494</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>495</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>21</v>
       </c>
@@ -9300,13 +9288,13 @@
         <v>21</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>212</v>
+        <v>21</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>464</v>
+        <v>21</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>465</v>
+        <v>21</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>21</v>
@@ -9324,45 +9312,45 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>460</v>
+        <v>491</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>104</v>
+        <v>497</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>466</v>
+        <v>21</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>467</v>
+        <v>498</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>468</v>
+        <v>499</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>469</v>
+        <v>21</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>470</v>
+        <v>500</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>470</v>
+        <v>500</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9385,20 +9373,16 @@
         <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>293</v>
+        <v>106</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>471</v>
+        <v>107</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>474</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>21</v>
       </c>
@@ -9422,13 +9406,13 @@
         <v>21</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>212</v>
+        <v>21</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>475</v>
+        <v>21</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>476</v>
+        <v>21</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>21</v>
@@ -9446,7 +9430,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>470</v>
+        <v>109</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9458,7 +9442,7 @@
         <v>21</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>21</v>
@@ -9467,10 +9451,10 @@
         <v>21</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>477</v>
+        <v>21</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>478</v>
+        <v>110</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>21</v>
@@ -9481,21 +9465,21 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>479</v>
+        <v>501</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>479</v>
+        <v>501</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>21</v>
@@ -9507,16 +9491,16 @@
         <v>21</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>480</v>
+        <v>113</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>481</v>
+        <v>114</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>482</v>
+        <v>115</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>483</v>
+        <v>116</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9566,79 +9550,81 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>479</v>
+        <v>120</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>484</v>
+        <v>21</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>485</v>
+        <v>21</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>486</v>
+        <v>110</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>487</v>
+        <v>21</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>488</v>
+        <v>502</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>488</v>
+        <v>502</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>21</v>
+        <v>503</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>489</v>
+        <v>113</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>490</v>
+        <v>504</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>491</v>
+        <v>505</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>21</v>
       </c>
@@ -9686,45 +9672,45 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>488</v>
+        <v>506</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>493</v>
+        <v>21</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>494</v>
+        <v>21</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>495</v>
+        <v>244</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>496</v>
+        <v>21</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9735,7 +9721,7 @@
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>21</v>
@@ -9747,20 +9733,16 @@
         <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>498</v>
+        <v>508</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>499</v>
+        <v>509</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>502</v>
-      </c>
+        <v>510</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>21</v>
       </c>
@@ -9808,19 +9790,19 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>21</v>
+        <v>511</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>503</v>
+        <v>104</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>21</v>
@@ -9829,10 +9811,10 @@
         <v>21</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>21</v>
@@ -9843,10 +9825,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9869,13 +9851,13 @@
         <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>106</v>
+        <v>508</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>107</v>
+        <v>515</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>108</v>
+        <v>516</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9926,7 +9908,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>109</v>
+        <v>514</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9935,10 +9917,10 @@
         <v>92</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>21</v>
+        <v>511</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>21</v>
@@ -9947,10 +9929,10 @@
         <v>21</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>21</v>
+        <v>512</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>110</v>
+        <v>517</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>21</v>
@@ -9961,21 +9943,21 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>507</v>
+        <v>518</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>507</v>
+        <v>518</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>21</v>
@@ -9987,18 +9969,20 @@
         <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>113</v>
+        <v>293</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>114</v>
+        <v>519</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>115</v>
+        <v>520</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="O65" s="2"/>
+        <v>521</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>522</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>21</v>
       </c>
@@ -10022,13 +10006,13 @@
         <v>21</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>21</v>
+        <v>225</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>21</v>
+        <v>523</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>21</v>
+        <v>524</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>21</v>
@@ -10046,31 +10030,31 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>120</v>
+        <v>518</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>21</v>
+        <v>525</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>21</v>
+        <v>526</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>110</v>
+        <v>444</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>21</v>
@@ -10081,14 +10065,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>508</v>
+        <v>527</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>508</v>
+        <v>527</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>509</v>
+        <v>21</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10101,25 +10085,25 @@
         <v>21</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>113</v>
+        <v>293</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>510</v>
+        <v>528</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>511</v>
+        <v>529</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>116</v>
+        <v>530</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>251</v>
+        <v>531</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>21</v>
@@ -10144,13 +10128,13 @@
         <v>21</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>21</v>
+        <v>212</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>21</v>
+        <v>532</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>21</v>
+        <v>533</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>21</v>
@@ -10168,7 +10152,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>512</v>
+        <v>527</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10180,19 +10164,19 @@
         <v>21</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>21</v>
+        <v>525</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>21</v>
+        <v>526</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>244</v>
+        <v>444</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>21</v>
@@ -10203,10 +10187,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>513</v>
+        <v>534</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>513</v>
+        <v>534</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10229,16 +10213,18 @@
         <v>21</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>514</v>
+        <v>535</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>515</v>
+        <v>536</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>516</v>
+        <v>537</v>
       </c>
       <c r="N67" s="2"/>
-      <c r="O67" s="2"/>
+      <c r="O67" t="s" s="2">
+        <v>538</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>21</v>
       </c>
@@ -10286,7 +10272,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>513</v>
+        <v>534</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10295,7 +10281,7 @@
         <v>92</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>517</v>
+        <v>21</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>104</v>
@@ -10307,10 +10293,10 @@
         <v>21</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>518</v>
+        <v>21</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>519</v>
+        <v>539</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>21</v>
@@ -10321,10 +10307,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10347,13 +10333,13 @@
         <v>21</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>514</v>
+        <v>106</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>521</v>
+        <v>541</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>522</v>
+        <v>542</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10404,7 +10390,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10413,7 +10399,7 @@
         <v>92</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>517</v>
+        <v>21</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>104</v>
@@ -10425,10 +10411,10 @@
         <v>21</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>523</v>
+        <v>543</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>21</v>
@@ -10439,10 +10425,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>524</v>
+        <v>544</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>524</v>
+        <v>544</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10453,7 +10439,7 @@
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>21</v>
@@ -10462,23 +10448,21 @@
         <v>21</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>293</v>
+        <v>545</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>525</v>
+        <v>546</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>526</v>
+        <v>547</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>528</v>
-      </c>
+        <v>548</v>
+      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>21</v>
       </c>
@@ -10502,13 +10486,13 @@
         <v>21</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>225</v>
+        <v>21</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>529</v>
+        <v>21</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>530</v>
+        <v>21</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>21</v>
@@ -10526,13 +10510,13 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>524</v>
+        <v>544</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>21</v>
@@ -10544,13 +10528,13 @@
         <v>21</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>531</v>
+        <v>21</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>532</v>
+        <v>549</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>450</v>
+        <v>550</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>21</v>
@@ -10561,10 +10545,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>533</v>
+        <v>551</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>533</v>
+        <v>551</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10584,23 +10568,21 @@
         <v>21</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>293</v>
+        <v>552</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>534</v>
+        <v>553</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>535</v>
+        <v>554</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>537</v>
-      </c>
+        <v>555</v>
+      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>21</v>
       </c>
@@ -10624,13 +10606,13 @@
         <v>21</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>212</v>
+        <v>21</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>538</v>
+        <v>21</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>539</v>
+        <v>21</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>21</v>
@@ -10648,7 +10630,7 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>533</v>
+        <v>551</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10666,13 +10648,13 @@
         <v>21</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>531</v>
+        <v>21</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>532</v>
+        <v>549</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>450</v>
+        <v>556</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>21</v>
@@ -10681,12 +10663,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
-        <v>540</v>
+        <v>557</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>540</v>
+        <v>557</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10697,29 +10679,31 @@
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>541</v>
+        <v>492</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>542</v>
+        <v>558</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="N71" s="2"/>
+        <v>559</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>560</v>
+      </c>
       <c r="O71" t="s" s="2">
-        <v>544</v>
+        <v>561</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>21</v>
@@ -10768,19 +10752,19 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>540</v>
+        <v>557</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>104</v>
+        <v>562</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>21</v>
@@ -10789,10 +10773,10 @@
         <v>21</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>21</v>
+        <v>563</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>545</v>
+        <v>564</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>21</v>
@@ -10803,10 +10787,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>546</v>
+        <v>565</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>546</v>
+        <v>565</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10832,10 +10816,10 @@
         <v>106</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>547</v>
+        <v>107</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>548</v>
+        <v>108</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10886,7 +10870,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>546</v>
+        <v>109</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10898,7 +10882,7 @@
         <v>21</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>21</v>
@@ -10907,10 +10891,10 @@
         <v>21</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>518</v>
+        <v>21</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>549</v>
+        <v>110</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>21</v>
@@ -10921,14 +10905,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>550</v>
+        <v>566</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>550</v>
+        <v>566</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10944,19 +10928,19 @@
         <v>21</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>551</v>
+        <v>113</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>552</v>
+        <v>114</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>553</v>
+        <v>115</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>554</v>
+        <v>116</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11006,7 +10990,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>550</v>
+        <v>120</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11018,7 +11002,7 @@
         <v>21</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>21</v>
@@ -11027,10 +11011,10 @@
         <v>21</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>555</v>
+        <v>21</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>556</v>
+        <v>110</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>21</v>
@@ -11041,14 +11025,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>557</v>
+        <v>567</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>557</v>
+        <v>567</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>21</v>
+        <v>503</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11061,24 +11045,26 @@
         <v>21</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="J74" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>558</v>
+        <v>113</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>559</v>
+        <v>504</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>560</v>
+        <v>505</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="O74" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>21</v>
       </c>
@@ -11126,7 +11112,7 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>557</v>
+        <v>506</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11138,7 +11124,7 @@
         <v>21</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>21</v>
@@ -11147,10 +11133,10 @@
         <v>21</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>555</v>
+        <v>21</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>562</v>
+        <v>244</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>21</v>
@@ -11159,12 +11145,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="75" hidden="true">
+    <row r="75">
       <c r="A75" t="s" s="2">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11172,10 +11158,10 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>93</v>
@@ -11187,19 +11173,19 @@
         <v>93</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>498</v>
+        <v>293</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>564</v>
+        <v>345</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>21</v>
@@ -11224,13 +11210,13 @@
         <v>21</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>21</v>
+        <v>150</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>21</v>
+        <v>572</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>21</v>
+        <v>573</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>21</v>
@@ -11248,45 +11234,45 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>568</v>
+        <v>104</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>21</v>
+        <v>574</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>569</v>
+        <v>352</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>570</v>
+        <v>353</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>21</v>
+        <v>354</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="76" hidden="true">
+    <row r="76">
       <c r="A76" t="s" s="2">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11300,25 +11286,29 @@
         <v>92</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>106</v>
+        <v>576</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>107</v>
+        <v>577</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
+        <v>578</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>417</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>21</v>
       </c>
@@ -11342,13 +11332,13 @@
         <v>21</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>21</v>
+        <v>150</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>21</v>
+        <v>418</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>21</v>
+        <v>419</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>21</v>
@@ -11366,7 +11356,7 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>109</v>
+        <v>575</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11375,50 +11365,50 @@
         <v>92</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>21</v>
+        <v>580</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>21</v>
+        <v>581</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>21</v>
+        <v>422</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>110</v>
+        <v>423</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>21</v>
+        <v>424</v>
       </c>
     </row>
-    <row r="77" hidden="true">
+    <row r="77">
       <c r="A77" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>21</v>
@@ -11427,18 +11417,20 @@
         <v>21</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>113</v>
+        <v>293</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>114</v>
+        <v>583</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>115</v>
+        <v>584</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="O77" s="2"/>
+        <v>585</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>429</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>21</v>
       </c>
@@ -11462,13 +11454,13 @@
         <v>21</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>21</v>
+        <v>150</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>21</v>
+        <v>430</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>21</v>
+        <v>431</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>21</v>
@@ -11486,19 +11478,19 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>120</v>
+        <v>582</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>21</v>
+        <v>586</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>21</v>
@@ -11507,10 +11499,10 @@
         <v>21</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>21</v>
+        <v>244</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>110</v>
+        <v>433</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>21</v>
@@ -11521,14 +11513,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>573</v>
+        <v>587</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>573</v>
+        <v>587</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>509</v>
+        <v>435</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -11541,25 +11533,25 @@
         <v>21</v>
       </c>
       <c r="I78" t="s" s="2">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>113</v>
+        <v>293</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>510</v>
+        <v>436</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>511</v>
+        <v>437</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>116</v>
+        <v>438</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>251</v>
+        <v>439</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>21</v>
@@ -11584,13 +11576,13 @@
         <v>21</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>21</v>
+        <v>150</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>21</v>
+        <v>440</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>21</v>
+        <v>441</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>21</v>
@@ -11608,7 +11600,7 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>512</v>
+        <v>587</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11620,33 +11612,33 @@
         <v>21</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>21</v>
+        <v>442</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>21</v>
+        <v>443</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>244</v>
+        <v>444</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>21</v>
+        <v>445</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>574</v>
+        <v>588</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>574</v>
+        <v>588</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11654,34 +11646,34 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>293</v>
+        <v>82</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>345</v>
+        <v>589</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>575</v>
+        <v>590</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>576</v>
+        <v>495</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>577</v>
+        <v>496</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>21</v>
@@ -11706,13 +11698,13 @@
         <v>21</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>150</v>
+        <v>21</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>349</v>
+        <v>21</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>350</v>
+        <v>21</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>21</v>
@@ -11730,13 +11722,13 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>574</v>
+        <v>588</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>21</v>
@@ -11748,521 +11740,33 @@
         <v>21</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>578</v>
+        <v>21</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>353</v>
+        <v>498</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>354</v>
+        <v>499</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>355</v>
+        <v>21</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="80" hidden="true">
-      <c r="A80" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="C80" s="2"/>
-      <c r="D80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E80" s="2"/>
-      <c r="F80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G80" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H80" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="I80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J80" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="K80" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="L80" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="P80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q80" s="2"/>
-      <c r="R80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X80" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="Z80" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="AG80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH80" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI80" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="AJ80" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="AO80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP80" t="s" s="2">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="81" hidden="true">
-      <c r="A81" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="C81" s="2"/>
-      <c r="D81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E81" s="2"/>
-      <c r="F81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G81" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H81" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="I81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K81" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="L81" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="P81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q81" s="2"/>
-      <c r="R81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X81" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="AG81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH81" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI81" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="AJ81" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="AO81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP81" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="82" hidden="true">
-      <c r="A82" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="C82" s="2"/>
-      <c r="D82" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="E82" s="2"/>
-      <c r="F82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K82" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="L82" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="P82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q82" s="2"/>
-      <c r="R82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ82" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AO82" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP82" t="s" s="2">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="83" hidden="true">
-      <c r="A83" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="C83" s="2"/>
-      <c r="D83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E83" s="2"/>
-      <c r="F83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="P83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q83" s="2"/>
-      <c r="R83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="AG83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ83" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP83" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP83">
-    <filterColumn colId="6">
+  <autoFilter ref="A1:AP79">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI82">
+  <conditionalFormatting sqref="A2:AI78">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/build/temp/pages/StructureDefinition-cibmtr-vital-signs.xlsx
+++ b/build/temp/pages/StructureDefinition-cibmtr-vital-signs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T07:35:08-05:00</t>
+    <t>2026-06-11T12:11:14-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/temp/pages/StructureDefinition-cibmtr-vital-signs.xlsx
+++ b/build/temp/pages/StructureDefinition-cibmtr-vital-signs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T12:11:14-05:00</t>
+    <t>2026-06-12T09:38:46-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/temp/pages/StructureDefinition-cibmtr-vital-signs.xlsx
+++ b/build/temp/pages/StructureDefinition-cibmtr-vital-signs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T09:38:46-05:00</t>
+    <t>2026-06-21T22:38:39-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/temp/pages/StructureDefinition-cibmtr-vital-signs.xlsx
+++ b/build/temp/pages/StructureDefinition-cibmtr-vital-signs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-21T22:38:39-05:00</t>
+    <t>2026-06-21T23:16:04-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/temp/pages/StructureDefinition-cibmtr-vital-signs.xlsx
+++ b/build/temp/pages/StructureDefinition-cibmtr-vital-signs.xlsx
@@ -60,19 +60,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-21T23:16:04-05:00</t>
+    <t>2026-06-22T08:51:47-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the National Marrow Donor Program</t>
+    <t>The Medical College of Wisconsin, Inc. and the NMDP</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the National Marrow Donor Program (http://www.cibmtr.org)</t>
+    <t>The Medical College of Wisconsin, Inc. and the NMDP (http://www.cibmtr.org)</t>
   </si>
   <si>
     <t>Bob Milius (bmilius@nmdp.org)</t>

--- a/build/temp/pages/StructureDefinition-cibmtr-vital-signs.xlsx
+++ b/build/temp/pages/StructureDefinition-cibmtr-vital-signs.xlsx
@@ -60,19 +60,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T08:51:47-05:00</t>
+    <t>2026-06-22T09:21:59-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the NMDP</t>
+    <t>The Medical College of Wisconsin, Inc. and NMDP</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the NMDP (http://www.cibmtr.org)</t>
+    <t>The Medical College of Wisconsin, Inc. and NMDP (http://www.cibmtr.org)</t>
   </si>
   <si>
     <t>Bob Milius (bmilius@nmdp.org)</t>

--- a/build/temp/pages/StructureDefinition-cibmtr-vital-signs.xlsx
+++ b/build/temp/pages/StructureDefinition-cibmtr-vital-signs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:21:59-05:00</t>
+    <t>2026-06-25T19:24:07-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/build/temp/pages/StructureDefinition-cibmtr-vital-signs.xlsx
+++ b/build/temp/pages/StructureDefinition-cibmtr-vital-signs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T19:24:07-05:00</t>
+    <t>2026-08-19T10:07:56-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -719,7 +719,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -837,7 +837,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -866,7 +866,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -946,7 +946,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t>value:coding.code}
@@ -1153,7 +1153,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1176,7 +1176,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1356,7 +1356,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t>obs-6
@@ -1388,7 +1388,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1444,7 +1444,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1477,7 +1477,7 @@
     <t>Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1489,7 +1489,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1517,7 +1517,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1597,7 +1597,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1647,7 +1647,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1680,7 +1680,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1717,7 +1717,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(QuestionnaireResponse|MolecularSequence|vitalsigns)
+    <t xml:space="preserve">Reference(QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
 </t>
   </si>
   <si>
@@ -1739,7 +1739,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|MolecularSequence|vitalsigns)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
 </t>
   </si>
   <si>

--- a/build/temp/pages/StructureDefinition-cibmtr-vital-signs.xlsx
+++ b/build/temp/pages/StructureDefinition-cibmtr-vital-signs.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.10</t>
+    <t>0.1.12</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,19 +60,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T10:10:52-05:00</t>
+    <t>2026-08-27T20:01:54-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the National Marrow Donor Program</t>
+    <t>The Medical College of Wisconsin, Inc. and NMDP</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>The Medical College of Wisconsin, Inc. and the National Marrow Donor Program (http://www.cibmtr.org)</t>
+    <t>The Medical College of Wisconsin, Inc. and NMDP (http://www.cibmtr.org)</t>
   </si>
   <si>
     <t>Bob Milius (bmilius@nmdp.org)</t>
@@ -719,7 +719,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -837,7 +837,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -866,7 +866,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -946,7 +946,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t>value:coding.code}
@@ -1153,7 +1153,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1176,7 +1176,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1356,7 +1356,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t>obs-6
@@ -1388,7 +1388,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1444,7 +1444,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1477,7 +1477,7 @@
     <t>Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1489,7 +1489,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1517,7 +1517,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1597,7 +1597,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1647,7 +1647,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1680,7 +1680,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1717,7 +1717,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(QuestionnaireResponse|MolecularSequence|vitalsigns)
+    <t xml:space="preserve">Reference(QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
 </t>
   </si>
   <si>
@@ -1739,7 +1739,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|MolecularSequence|vitalsigns)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
 </t>
   </si>
   <si>
